--- a/app/reports/YQ_research.xlsx
+++ b/app/reports/YQ_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-06 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-07 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1.966</v>
+        <v>2.2</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04668000221252441</v>
+        <v>0.04654000282287598</v>
       </c>
     </row>
     <row r="6">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>9686276.703967446</v>
+        <v>9686277.272727272</v>
       </c>
     </row>
     <row r="36">
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>1.966</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="38">
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>19043220</v>
+        <v>21309810</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n">
@@ -1531,14 +1531,14 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>7950789</v>
+        <v>7745679</v>
       </c>
       <c r="D7" s="33" t="n"/>
       <c r="E7" s="33" t="n">
-        <v>-0.842</v>
+        <v>-0.762</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>0.28</v>
+        <v>0.253</v>
       </c>
     </row>
     <row r="8">
@@ -1553,14 +1553,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>16275165</v>
+        <v>21563048</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>210.606</v>
+        <v>217.504</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>26.175</v>
+        <v>27.033</v>
       </c>
     </row>
     <row r="9">
@@ -1591,14 +1591,14 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>30078174</v>
+        <v>30654018</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n">
-        <v>-2.337</v>
+        <v>-2.324</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>6.861</v>
+        <v>6.823</v>
       </c>
     </row>
     <row r="11">
@@ -1613,14 +1613,14 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>46230884</v>
+        <v>46441024</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
-        <v>-11.18</v>
+        <v>-11.236</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>0.505</v>
+        <v>0.508</v>
       </c>
     </row>
     <row r="12">
@@ -1651,14 +1651,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>6743035</v>
+        <v>6803484</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>0.09</v>
+        <v>0.095</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>-0.02</v>
+        <v>-0.022</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/YQ_research.xlsx
+++ b/app/reports/YQ_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-07 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-08 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>2.2</v>
+        <v>2.3981</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04654000282287598</v>
+        <v>0.04659999847412109</v>
       </c>
     </row>
     <row r="6">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>9686277.272727272</v>
+        <v>9686276.635669906</v>
       </c>
     </row>
     <row r="36">
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>2.2</v>
+        <v>2.3981</v>
       </c>
     </row>
     <row r="38">
@@ -1493,14 +1493,14 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>21309810</v>
+        <v>23228660</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>-1.73</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="6">
@@ -1531,14 +1531,14 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>7745679</v>
+        <v>7723758</v>
       </c>
       <c r="D7" s="33" t="n"/>
       <c r="E7" s="33" t="n">
-        <v>-0.762</v>
+        <v>-0.739</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>0.253</v>
+        <v>0.246</v>
       </c>
     </row>
     <row r="8">
@@ -1553,14 +1553,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>21563048</v>
+        <v>21858616</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>217.504</v>
+        <v>289.624</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>27.033</v>
+        <v>35.996</v>
       </c>
     </row>
     <row r="9">
@@ -1591,14 +1591,14 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>30654018</v>
+        <v>30423680</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n">
-        <v>-2.324</v>
+        <v>-2.35</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>6.823</v>
+        <v>6.899</v>
       </c>
     </row>
     <row r="11">
@@ -1613,14 +1613,14 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>46441024</v>
+        <v>46117132</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
-        <v>-11.236</v>
+        <v>-16.66</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>0.508</v>
+        <v>0.514</v>
       </c>
     </row>
     <row r="12">
@@ -1651,14 +1651,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>6803484</v>
+        <v>6634902</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>0.095</v>
+        <v>0.091</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>-0.022</v>
+        <v>-0.021</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/YQ_research.xlsx
+++ b/app/reports/YQ_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-08 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-09 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/YQ_research.xlsx
+++ b/app/reports/YQ_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-09 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-10 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>2.3981</v>
+        <v>2.4481</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04659999847412109</v>
+        <v>0.04699999809265137</v>
       </c>
     </row>
     <row r="6">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>9686276.635669906</v>
+        <v>9686277.521343082</v>
       </c>
     </row>
     <row r="36">
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>2.3981</v>
+        <v>2.4481</v>
       </c>
     </row>
     <row r="38">
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>23228660</v>
+        <v>23712976</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n">
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>7723758</v>
+        <v>7600065</v>
       </c>
       <c r="D7" s="33" t="n"/>
       <c r="E7" s="33" t="n">
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>21858616</v>
+        <v>22001172</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
@@ -1591,7 +1591,7 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>30423680</v>
+        <v>30749990</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n">
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>46117132</v>
+        <v>45694388</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>6634902</v>
+        <v>6189364</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">

--- a/app/reports/YQ_research.xlsx
+++ b/app/reports/YQ_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-10 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-13 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>2.4481</v>
+        <v>2.24</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04699999809265137</v>
+        <v>0.04644999980926514</v>
       </c>
     </row>
     <row r="6">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>9686277.521343082</v>
+        <v>9686276.785714285</v>
       </c>
     </row>
     <row r="36">
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>2.4481</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="38">
@@ -1493,11 +1493,11 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>23712976</v>
+        <v>21697260</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="F5" s="31" t="n">
         <v>-1.7</v>
@@ -1531,14 +1531,14 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>7600065</v>
+        <v>7629016</v>
       </c>
       <c r="D7" s="33" t="n"/>
       <c r="E7" s="33" t="n">
-        <v>-0.739</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>0.246</v>
+        <v>0.227</v>
       </c>
     </row>
     <row r="8">
@@ -1553,14 +1553,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>22001172</v>
+        <v>20200212</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>289.624</v>
+        <v>275.827</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>35.996</v>
+        <v>34.281</v>
       </c>
     </row>
     <row r="9">
@@ -1591,14 +1591,14 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>30749990</v>
+        <v>30154954</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n">
-        <v>-2.35</v>
+        <v>-2.3</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>6.899</v>
+        <v>6.752</v>
       </c>
     </row>
     <row r="11">
@@ -1613,14 +1613,14 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>45694388</v>
+        <v>44195584</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
-        <v>-16.66</v>
+        <v>-16.311</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>0.514</v>
+        <v>0.503</v>
       </c>
     </row>
     <row r="12">
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>6189364</v>
+        <v>6309539</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">

--- a/app/reports/YQ_research.xlsx
+++ b/app/reports/YQ_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-13 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-15 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>2.24</v>
+        <v>2.325</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04644999980926514</v>
+        <v>0.04696000099182129</v>
       </c>
     </row>
     <row r="6">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>9686276.785714285</v>
+        <v>9686276.989247311</v>
       </c>
     </row>
     <row r="36">
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>2.24</v>
+        <v>2.325</v>
       </c>
     </row>
     <row r="38">
@@ -1493,14 +1493,14 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>21697260</v>
+        <v>22520594</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>-1.7</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="6">
@@ -1531,14 +1531,14 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>7629016</v>
+        <v>7561112</v>
       </c>
       <c r="D7" s="33" t="n"/>
       <c r="E7" s="33" t="n">
-        <v>-0.6830000000000001</v>
+        <v>-0.642</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>0.227</v>
+        <v>0.213</v>
       </c>
     </row>
     <row r="8">
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>20200212</v>
+        <v>20813204</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
@@ -1591,14 +1591,14 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>30154954</v>
+        <v>30769186</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n">
-        <v>-2.3</v>
+        <v>-2.362</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>6.752</v>
+        <v>6.933</v>
       </c>
     </row>
     <row r="11">
@@ -1613,14 +1613,14 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>44195584</v>
+        <v>43982080</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
-        <v>-16.311</v>
+        <v>-16.224</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>0.503</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12">
@@ -1651,14 +1651,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>6309539</v>
+        <v>4503545</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>0.091</v>
+        <v>0.107</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>-0.021</v>
+        <v>-0.024</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/YQ_research.xlsx
+++ b/app/reports/YQ_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-15 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-16 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
